--- a/docentes/Martínez Castillo Columba - Estadisticos 20212.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20212.xlsx
@@ -523,22 +523,22 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>26</v>
       </c>
       <c r="G4">
-        <v>89.66</v>
+        <v>86.67</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -552,10 +552,10 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>31</v>
@@ -564,7 +564,7 @@
         <v>88.56999999999999</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -617,16 +617,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>75.76000000000001</v>
+      </c>
+      <c r="H2">
+        <v>9.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -640,16 +643,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>29.03</v>
+      </c>
+      <c r="H3">
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -660,19 +666,22 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H4">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -686,16 +695,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H5">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -760,7 +772,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -786,7 +798,7 @@
         <v>83.87</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -797,7 +809,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -806,10 +818,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>89.66</v>
+        <v>90</v>
       </c>
       <c r="H4">
         <v>8.4</v>
@@ -826,19 +838,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>88.56999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20212.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -74,6 +74,24 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>OLIVERA</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>JARED JESUS</t>
   </si>
 </sst>
 </file>
@@ -860,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -890,6 +908,52 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920204</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920145</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20212.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -76,16 +76,25 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>OLIVERA</t>
   </si>
   <si>
     <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
   </si>
   <si>
     <t>CRISTHIAN</t>
@@ -878,7 +887,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -910,22 +919,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920204</v>
+        <v>20330051920070</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -933,24 +942,47 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920145</v>
+        <v>20330051920204</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920145</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="G3">
+      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20212.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -79,25 +79,16 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>OLIVERA</t>
-  </si>
-  <si>
     <t>ESPINOSA</t>
   </si>
   <si>
     <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
   </si>
   <si>
     <t>JARED JESUS</t>
@@ -527,19 +518,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>83.87</v>
+        <v>93.55</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -553,19 +544,19 @@
         <v>30</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="F4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>86.67</v>
+        <v>90</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -579,19 +570,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>88.56999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -644,19 +635,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>75.76000000000001</v>
+        <v>93.94</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -670,19 +661,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>29.03</v>
+        <v>77.42</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -696,19 +687,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -722,19 +713,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>80</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -799,7 +790,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -813,19 +804,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>83.87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -839,10 +830,10 @@
         <v>30</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>3</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>27</v>
@@ -851,7 +842,7 @@
         <v>90</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -865,19 +856,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>91.43000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -887,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -925,10 +916,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -942,47 +933,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920204</v>
+        <v>19330051920145</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920145</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
         <v>1</v>
       </c>
     </row>
